--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/113.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/113.xlsx
@@ -426,13 +426,13 @@
         <v>-7.781329143536314</v>
       </c>
       <c r="E2">
-        <v>-9.269779313460809</v>
+        <v>-9.341206933983793</v>
       </c>
       <c r="F2">
-        <v>-6.525994239692772</v>
+        <v>-6.648014029359635</v>
       </c>
       <c r="G2">
-        <v>-9.270055037368401</v>
+        <v>-10.40733336756531</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.652320055197887</v>
       </c>
       <c r="E3">
-        <v>-9.289582330296351</v>
+        <v>-9.291493346327588</v>
       </c>
       <c r="F3">
-        <v>-6.718146070265998</v>
+        <v>-6.734452302297842</v>
       </c>
       <c r="G3">
-        <v>-9.202943658196297</v>
+        <v>-8.798335403477651</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.581586059880804</v>
       </c>
       <c r="E4">
-        <v>-10.53501683730788</v>
+        <v>-11.18647857957733</v>
       </c>
       <c r="F4">
-        <v>-6.611762605028748</v>
+        <v>-6.551246826440933</v>
       </c>
       <c r="G4">
-        <v>-9.49014341536469</v>
+        <v>-9.294771570364601</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.553514796543349</v>
       </c>
       <c r="E5">
-        <v>-11.38572690744081</v>
+        <v>-11.80581079876236</v>
       </c>
       <c r="F5">
-        <v>-6.771516959616307</v>
+        <v>-6.952336582511607</v>
       </c>
       <c r="G5">
-        <v>-9.395789556949921</v>
+        <v>-9.193124580126819</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.53330295983706</v>
       </c>
       <c r="E6">
-        <v>-11.70123022002922</v>
+        <v>-11.37293396836914</v>
       </c>
       <c r="F6">
-        <v>-6.303476827823389</v>
+        <v>-6.262383222656045</v>
       </c>
       <c r="G6">
-        <v>-9.050125565557998</v>
+        <v>-9.838581643918522</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.498567358172436</v>
       </c>
       <c r="E7">
-        <v>-12.5190816827625</v>
+        <v>-13.02562319983848</v>
       </c>
       <c r="F7">
-        <v>-6.221119765029271</v>
+        <v>-6.756475316757943</v>
       </c>
       <c r="G7">
-        <v>-9.963104503832668</v>
+        <v>-9.548213694669045</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.419347509157224</v>
       </c>
       <c r="E8">
-        <v>-12.77782963061277</v>
+        <v>-14.39825348477745</v>
       </c>
       <c r="F8">
-        <v>-6.150673754425172</v>
+        <v>-6.812184547892398</v>
       </c>
       <c r="G8">
-        <v>-9.485968817439669</v>
+        <v>-9.331379582937862</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.288678589143738</v>
       </c>
       <c r="E9">
-        <v>-13.76285876828721</v>
+        <v>-13.91234822375442</v>
       </c>
       <c r="F9">
-        <v>-6.183586726686314</v>
+        <v>-6.562512914396891</v>
       </c>
       <c r="G9">
-        <v>-8.982861901291088</v>
+        <v>-9.653750575915472</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-7.095752538873958</v>
       </c>
       <c r="E10">
-        <v>-14.77228732391499</v>
+        <v>-15.23128439238444</v>
       </c>
       <c r="F10">
-        <v>-6.420455681561409</v>
+        <v>-6.431023751135136</v>
       </c>
       <c r="G10">
-        <v>-8.631427629024214</v>
+        <v>-8.407932699668017</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.837128284335339</v>
       </c>
       <c r="E11">
-        <v>-16.2366282644573</v>
+        <v>-15.85215176425807</v>
       </c>
       <c r="F11">
-        <v>-6.225470205178983</v>
+        <v>-6.665706004067489</v>
       </c>
       <c r="G11">
-        <v>-8.415606544228048</v>
+        <v>-8.934600768419592</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.52194966597101</v>
       </c>
       <c r="E12">
-        <v>-15.59454952033174</v>
+        <v>-16.56967941382543</v>
       </c>
       <c r="F12">
-        <v>-6.432917467483523</v>
+        <v>-6.925261150254775</v>
       </c>
       <c r="G12">
-        <v>-8.660798789048629</v>
+        <v>-9.231023705460395</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-6.156124825029017</v>
       </c>
       <c r="E13">
-        <v>-16.80064970211264</v>
+        <v>-17.08510126843045</v>
       </c>
       <c r="F13">
-        <v>-6.282938141732534</v>
+        <v>-6.363781577597972</v>
       </c>
       <c r="G13">
-        <v>-8.208419362198299</v>
+        <v>-8.482459700848089</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-5.766173382467433</v>
       </c>
       <c r="E14">
-        <v>-17.70057975623495</v>
+        <v>-18.33340229948883</v>
       </c>
       <c r="F14">
-        <v>-6.428169121222557</v>
+        <v>-6.10819717806717</v>
       </c>
       <c r="G14">
-        <v>-7.485171099324802</v>
+        <v>-8.189817406813136</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-5.374967526349542</v>
       </c>
       <c r="E15">
-        <v>-18.80351224317311</v>
+        <v>-18.50423898142819</v>
       </c>
       <c r="F15">
-        <v>-6.184596339207406</v>
+        <v>-6.632994162457608</v>
       </c>
       <c r="G15">
-        <v>-6.40882004923264</v>
+        <v>-7.436400142440259</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-5.008782120801087</v>
       </c>
       <c r="E16">
-        <v>-19.62586500907001</v>
+        <v>-19.22372293176686</v>
       </c>
       <c r="F16">
-        <v>-5.993831835016105</v>
+        <v>-6.152513228845955</v>
       </c>
       <c r="G16">
-        <v>-6.183077259455277</v>
+        <v>-6.670962287214289</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.70298902428529</v>
       </c>
       <c r="E17">
-        <v>-20.35076501432185</v>
+        <v>-20.30607350434015</v>
       </c>
       <c r="F17">
-        <v>-5.797743703390054</v>
+        <v>-6.131958705695945</v>
       </c>
       <c r="G17">
-        <v>-5.313906770301783</v>
+        <v>-6.382405206374795</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-4.476616048641202</v>
       </c>
       <c r="E18">
-        <v>-20.84315505012387</v>
+        <v>-20.87755333868613</v>
       </c>
       <c r="F18">
-        <v>-5.711863290860562</v>
+        <v>-5.486918453749289</v>
       </c>
       <c r="G18">
-        <v>-4.850360873347492</v>
+        <v>-5.289220032215439</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-4.352330863759331</v>
       </c>
       <c r="E19">
-        <v>-22.27971833110312</v>
+        <v>-22.17530983438228</v>
       </c>
       <c r="F19">
-        <v>-5.521590527356005</v>
+        <v>-5.178835390901107</v>
       </c>
       <c r="G19">
-        <v>-4.355258856312869</v>
+        <v>-5.322312245425993</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-4.332150391582271</v>
       </c>
       <c r="E20">
-        <v>-22.31633557192915</v>
+        <v>-22.55369100856718</v>
       </c>
       <c r="F20">
-        <v>-5.025804263851066</v>
+        <v>-4.794475508194657</v>
       </c>
       <c r="G20">
-        <v>-3.948531852449089</v>
+        <v>-5.073878976522465</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-4.40467111213012</v>
       </c>
       <c r="E21">
-        <v>-22.78062189803956</v>
+        <v>-23.12446440096796</v>
       </c>
       <c r="F21">
-        <v>-4.972749323830888</v>
+        <v>-4.81999138605126</v>
       </c>
       <c r="G21">
-        <v>-4.830116887374849</v>
+        <v>-5.164266801381187</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-4.559580789814686</v>
       </c>
       <c r="E22">
-        <v>-24.17435487185427</v>
+        <v>-24.0474398593153</v>
       </c>
       <c r="F22">
-        <v>-4.532363468806894</v>
+        <v>-4.450264154150513</v>
       </c>
       <c r="G22">
-        <v>-4.104077834611746</v>
+        <v>-4.97646948457495</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-4.769502522304357</v>
       </c>
       <c r="E23">
-        <v>-24.13007092453326</v>
+        <v>-25.02291391683357</v>
       </c>
       <c r="F23">
-        <v>-4.326685997862858</v>
+        <v>-4.243380691151869</v>
       </c>
       <c r="G23">
-        <v>-4.138441297309381</v>
+        <v>-4.839730711620893</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-5.01722397104707</v>
       </c>
       <c r="E24">
-        <v>-24.07523563277438</v>
+        <v>-25.92490895510337</v>
       </c>
       <c r="F24">
-        <v>-4.043089404026243</v>
+        <v>-4.229137632001365</v>
       </c>
       <c r="G24">
-        <v>-3.904514838958939</v>
+        <v>-5.645110298778169</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-5.28007547417096</v>
       </c>
       <c r="E25">
-        <v>-24.17041962794161</v>
+        <v>-25.52662966612876</v>
       </c>
       <c r="F25">
-        <v>-3.982279847991114</v>
+        <v>-3.734496387873289</v>
       </c>
       <c r="G25">
-        <v>-5.247675996243124</v>
+        <v>-4.88475744150052</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-5.534553698935186</v>
       </c>
       <c r="E26">
-        <v>-25.13743902448755</v>
+        <v>-25.70309976973367</v>
       </c>
       <c r="F26">
-        <v>-4.041500155140099</v>
+        <v>-3.772769808731714</v>
       </c>
       <c r="G26">
-        <v>-5.518332957351779</v>
+        <v>-5.839392974295838</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-5.769532813767858</v>
       </c>
       <c r="E27">
-        <v>-25.44889388131309</v>
+        <v>-25.33807759387139</v>
       </c>
       <c r="F27">
-        <v>-3.906735492118737</v>
+        <v>-3.833276876936993</v>
       </c>
       <c r="G27">
-        <v>-5.053320488723592</v>
+        <v>-6.019791221821804</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-5.967950501876804</v>
       </c>
       <c r="E28">
-        <v>-24.90847032171172</v>
+        <v>-25.91563464033566</v>
       </c>
       <c r="F28">
-        <v>-4.140693991447733</v>
+        <v>-3.654638017087255</v>
       </c>
       <c r="G28">
-        <v>-5.63438744177647</v>
+        <v>-5.985907788227363</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-6.127920200983957</v>
       </c>
       <c r="E29">
-        <v>-24.76516676173899</v>
+        <v>-26.35317127048276</v>
       </c>
       <c r="F29">
-        <v>-4.028923946465595</v>
+        <v>-3.589143858954257</v>
       </c>
       <c r="G29">
-        <v>-6.255608001675169</v>
+        <v>-6.03552624476996</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-6.249622616774232</v>
       </c>
       <c r="E30">
-        <v>-23.85009349053503</v>
+        <v>-25.04153953042711</v>
       </c>
       <c r="F30">
-        <v>-3.582660958789405</v>
+        <v>-4.028980168025592</v>
       </c>
       <c r="G30">
-        <v>-5.666039567677442</v>
+        <v>-6.074610545406595</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-6.333941660340119</v>
       </c>
       <c r="E31">
-        <v>-24.60856760207975</v>
+        <v>-24.85707667019867</v>
       </c>
       <c r="F31">
-        <v>-3.783086860917845</v>
+        <v>-3.50514330534639</v>
       </c>
       <c r="G31">
-        <v>-6.260395050524955</v>
+        <v>-6.923599948952691</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.39410476021527</v>
       </c>
       <c r="E32">
-        <v>-24.00185171148009</v>
+        <v>-24.49057368333589</v>
       </c>
       <c r="F32">
-        <v>-3.650644702621474</v>
+        <v>-3.500402481688523</v>
       </c>
       <c r="G32">
-        <v>-5.731154687889367</v>
+        <v>-7.277791905653777</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.43322774189817</v>
       </c>
       <c r="E33">
-        <v>-23.9039778027523</v>
+        <v>-23.52232254185985</v>
       </c>
       <c r="F33">
-        <v>-3.923141893549732</v>
+        <v>-3.909680393268497</v>
       </c>
       <c r="G33">
-        <v>-5.668284117553068</v>
+        <v>-6.602784912378539</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-6.460847074982284</v>
       </c>
       <c r="E34">
-        <v>-22.81679534841283</v>
+        <v>-24.94732915717154</v>
       </c>
       <c r="F34">
-        <v>-4.078838397655457</v>
+        <v>-4.138438794224148</v>
       </c>
       <c r="G34">
-        <v>-5.293384698503841</v>
+        <v>-7.073339234239467</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.482228328005898</v>
       </c>
       <c r="E35">
-        <v>-22.29379282831896</v>
+        <v>-23.57005718637471</v>
       </c>
       <c r="F35">
-        <v>-4.188632769508086</v>
+        <v>-4.036028451202256</v>
       </c>
       <c r="G35">
-        <v>-5.412110793178724</v>
+        <v>-6.651400273622736</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.494692840983237</v>
       </c>
       <c r="E36">
-        <v>-22.29680879200807</v>
+        <v>-23.14397759546701</v>
       </c>
       <c r="F36">
-        <v>-4.291851594399809</v>
+        <v>-4.090912571554767</v>
       </c>
       <c r="G36">
-        <v>-5.478242250871205</v>
+        <v>-5.739245661187345</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-6.505331167287352</v>
       </c>
       <c r="E37">
-        <v>-21.66193937850273</v>
+        <v>-21.90976011857249</v>
       </c>
       <c r="F37">
-        <v>-4.345536057521375</v>
+        <v>-4.520871306831507</v>
       </c>
       <c r="G37">
-        <v>-4.599153367282056</v>
+        <v>-6.069101797629248</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-6.509298524668041</v>
       </c>
       <c r="E38">
-        <v>-21.49859279257205</v>
+        <v>-21.91772117587797</v>
       </c>
       <c r="F38">
-        <v>-4.457344903298443</v>
+        <v>-4.473689540198736</v>
       </c>
       <c r="G38">
-        <v>-4.552537575543578</v>
+        <v>-4.672164138605142</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.509452345856087</v>
       </c>
       <c r="E39">
-        <v>-20.87726804482364</v>
+        <v>-21.72872984164186</v>
       </c>
       <c r="F39">
-        <v>-4.469469755787047</v>
+        <v>-4.270504030512643</v>
       </c>
       <c r="G39">
-        <v>-5.077159727151883</v>
+        <v>-5.31719414202228</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.508013180257165</v>
       </c>
       <c r="E40">
-        <v>-20.61142850667736</v>
+        <v>-21.85722076313549</v>
       </c>
       <c r="F40">
-        <v>-4.490115737953674</v>
+        <v>-4.140789013802659</v>
       </c>
       <c r="G40">
-        <v>-4.721769352965582</v>
+        <v>-5.157506667389995</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.498916499282853</v>
       </c>
       <c r="E41">
-        <v>-20.39259000025669</v>
+        <v>-20.59993071117189</v>
       </c>
       <c r="F41">
-        <v>-4.503547939675474</v>
+        <v>-4.524833739031937</v>
       </c>
       <c r="G41">
-        <v>-4.50678914673639</v>
+        <v>-4.606463051832766</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-6.488559196928938</v>
       </c>
       <c r="E42">
-        <v>-19.02640826230465</v>
+        <v>-20.33799924609423</v>
       </c>
       <c r="F42">
-        <v>-4.698282794596781</v>
+        <v>-4.5493352532497</v>
       </c>
       <c r="G42">
-        <v>-4.606575610381102</v>
+        <v>-5.282569146227043</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-6.471178505862985</v>
       </c>
       <c r="E43">
-        <v>-18.98360512598415</v>
+        <v>-19.76564541626477</v>
       </c>
       <c r="F43">
-        <v>-4.543889680459462</v>
+        <v>-4.377185628388475</v>
       </c>
       <c r="G43">
-        <v>-3.822029286302459</v>
+        <v>-4.968841987652469</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-6.448120571127162</v>
       </c>
       <c r="E44">
-        <v>-18.01572079090274</v>
+        <v>-19.49158669779457</v>
       </c>
       <c r="F44">
-        <v>-4.355583879701881</v>
+        <v>-4.476578219788497</v>
       </c>
       <c r="G44">
-        <v>-3.499393449681707</v>
+        <v>-5.938017436456266</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-6.422583379478876</v>
       </c>
       <c r="E45">
-        <v>-17.70467349673789</v>
+        <v>-18.56469410943059</v>
       </c>
       <c r="F45">
-        <v>-4.436577767629285</v>
+        <v>-4.56200014945547</v>
       </c>
       <c r="G45">
-        <v>-3.993204353956015</v>
+        <v>-5.220741397735614</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-6.388937639486018</v>
       </c>
       <c r="E46">
-        <v>-16.59793256315928</v>
+        <v>-18.48161019681186</v>
       </c>
       <c r="F46">
-        <v>-4.626165578325415</v>
+        <v>-4.479573799527551</v>
       </c>
       <c r="G46">
-        <v>-3.882466605667394</v>
+        <v>-3.521021243689765</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.354498948145532</v>
       </c>
       <c r="E47">
-        <v>-16.62633515213539</v>
+        <v>-17.54642597253984</v>
       </c>
       <c r="F47">
-        <v>-4.34227045592374</v>
+        <v>-4.542860271614426</v>
       </c>
       <c r="G47">
-        <v>-4.377717597251285</v>
+        <v>-4.182193467156389</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.314400097515134</v>
       </c>
       <c r="E48">
-        <v>-15.17093794775823</v>
+        <v>-16.98216452576209</v>
       </c>
       <c r="F48">
-        <v>-4.651772519272155</v>
+        <v>-4.861964343928152</v>
       </c>
       <c r="G48">
-        <v>-3.679761902297819</v>
+        <v>-4.196067963511474</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.268465114101246</v>
       </c>
       <c r="E49">
-        <v>-15.41181653717423</v>
+        <v>-15.62490841007916</v>
       </c>
       <c r="F49">
-        <v>-4.644576951445356</v>
+        <v>-4.735848298911004</v>
       </c>
       <c r="G49">
-        <v>-3.786480648301765</v>
+        <v>-4.573509881534861</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.218657026738174</v>
       </c>
       <c r="E50">
-        <v>-14.68939813567859</v>
+        <v>-15.89668024917549</v>
       </c>
       <c r="F50">
-        <v>-4.718066448892451</v>
+        <v>-5.19657606456586</v>
       </c>
       <c r="G50">
-        <v>-4.295960364613443</v>
+        <v>-3.879480493590971</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.157616317898055</v>
       </c>
       <c r="E51">
-        <v>-14.18144373471222</v>
+        <v>-16.48673135542693</v>
       </c>
       <c r="F51">
-        <v>-4.670848257023623</v>
+        <v>-4.840043478499597</v>
       </c>
       <c r="G51">
-        <v>-3.715161565749245</v>
+        <v>-5.031573515076118</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.091791451492391</v>
       </c>
       <c r="E52">
-        <v>-13.88099306972531</v>
+        <v>-15.32699821901056</v>
       </c>
       <c r="F52">
-        <v>-4.693058940634704</v>
+        <v>-4.925411562165444</v>
       </c>
       <c r="G52">
-        <v>-3.818288369843082</v>
+        <v>-4.066287957280966</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.018152455585688</v>
       </c>
       <c r="E53">
-        <v>-11.89706860696493</v>
+        <v>-15.25303918151729</v>
       </c>
       <c r="F53">
-        <v>-4.913811708187809</v>
+        <v>-4.786606073500839</v>
       </c>
       <c r="G53">
-        <v>-3.464924049526815</v>
+        <v>-4.129201564709275</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.937492873803297</v>
       </c>
       <c r="E54">
-        <v>-12.50295125834717</v>
+        <v>-13.83761934567984</v>
       </c>
       <c r="F54">
-        <v>-4.675645302241489</v>
+        <v>-5.129269355012641</v>
       </c>
       <c r="G54">
-        <v>-4.197137269720659</v>
+        <v>-5.203460350020618</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.853954138648158</v>
       </c>
       <c r="E55">
-        <v>-12.27789968558798</v>
+        <v>-14.26635262235603</v>
       </c>
       <c r="F55">
-        <v>-4.954725166807271</v>
+        <v>-5.244033396027919</v>
       </c>
       <c r="G55">
-        <v>-4.005522893907643</v>
+        <v>-4.26853580536612</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.761781664689483</v>
       </c>
       <c r="E56">
-        <v>-11.49761191474832</v>
+        <v>-12.40265461602529</v>
       </c>
       <c r="F56">
-        <v>-4.889217547173992</v>
+        <v>-5.18115076894948</v>
       </c>
       <c r="G56">
-        <v>-4.104375783710281</v>
+        <v>-5.274368924926268</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.66796100815252</v>
       </c>
       <c r="E57">
-        <v>-11.43697111931161</v>
+        <v>-12.59054100260354</v>
       </c>
       <c r="F57">
-        <v>-4.649552163578709</v>
+        <v>-5.252142762167926</v>
       </c>
       <c r="G57">
-        <v>-4.490646926686903</v>
+        <v>-4.780577883925195</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.57082246585964</v>
       </c>
       <c r="E58">
-        <v>-10.32645796688462</v>
+        <v>-12.76868664159128</v>
       </c>
       <c r="F58">
-        <v>-5.144870441985635</v>
+        <v>-5.037594954391514</v>
       </c>
       <c r="G58">
-        <v>-4.650629039872183</v>
+        <v>-4.741086386187229</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-5.470375122123204</v>
       </c>
       <c r="E59">
-        <v>-10.60471910923394</v>
+        <v>-11.26604386789209</v>
       </c>
       <c r="F59">
-        <v>-4.802713946366773</v>
+        <v>-4.947615119099906</v>
       </c>
       <c r="G59">
-        <v>-4.913890242246107</v>
+        <v>-4.807115216967993</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-5.370563882514925</v>
       </c>
       <c r="E60">
-        <v>-10.60246392917812</v>
+        <v>-10.94809517933955</v>
       </c>
       <c r="F60">
-        <v>-5.270836826793773</v>
+        <v>-5.337259828446177</v>
       </c>
       <c r="G60">
-        <v>-4.873829330675386</v>
+        <v>-5.207876617770006</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.264794260943985</v>
       </c>
       <c r="E61">
-        <v>-9.641825152508982</v>
+        <v>-10.88240060691028</v>
       </c>
       <c r="F61">
-        <v>-5.198912030791133</v>
+        <v>-5.414984947364114</v>
       </c>
       <c r="G61">
-        <v>-4.815315438268768</v>
+        <v>-5.225978680778741</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.157858409791038</v>
       </c>
       <c r="E62">
-        <v>-8.762409085641421</v>
+        <v>-10.89421539559629</v>
       </c>
       <c r="F62">
-        <v>-5.179917062041352</v>
+        <v>-5.102594204425936</v>
       </c>
       <c r="G62">
-        <v>-4.828809221886837</v>
+        <v>-5.894016975693813</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.04705248903664</v>
       </c>
       <c r="E63">
-        <v>-9.303050011995163</v>
+        <v>-10.68394929047214</v>
       </c>
       <c r="F63">
-        <v>-5.102481761305941</v>
+        <v>-5.407792546949146</v>
       </c>
       <c r="G63">
-        <v>-5.03883685198928</v>
+        <v>-5.410376067316146</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.929772965084084</v>
       </c>
       <c r="E64">
-        <v>-8.81341781686382</v>
+        <v>-9.785350607708086</v>
       </c>
       <c r="F64">
-        <v>-5.300572489062064</v>
+        <v>-5.553931385855194</v>
       </c>
       <c r="G64">
-        <v>-5.36570687635476</v>
+        <v>-5.452535864758764</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.808165979642784</v>
       </c>
       <c r="E65">
-        <v>-8.446978228637143</v>
+        <v>-9.917536763991984</v>
       </c>
       <c r="F65">
-        <v>-5.225564217642064</v>
+        <v>-5.235402990641731</v>
       </c>
       <c r="G65">
-        <v>-5.247675996243124</v>
+        <v>-5.698327318321954</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.675463260939884</v>
       </c>
       <c r="E66">
-        <v>-8.768255345585324</v>
+        <v>-8.783144968122544</v>
       </c>
       <c r="F66">
-        <v>-5.643520045785688</v>
+        <v>-5.784270325314454</v>
       </c>
       <c r="G66">
-        <v>-4.874464955418926</v>
+        <v>-5.636926630205091</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.536839156874665</v>
       </c>
       <c r="E67">
-        <v>-9.094323588033621</v>
+        <v>-8.778688949698996</v>
       </c>
       <c r="F67">
-        <v>-5.413095586206995</v>
+        <v>-5.792908649230218</v>
       </c>
       <c r="G67">
-        <v>-5.689726521010927</v>
+        <v>-5.67045252488129</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.39377151776575</v>
       </c>
       <c r="E68">
-        <v>-7.243613245156876</v>
+        <v>-9.145921020877017</v>
       </c>
       <c r="F68">
-        <v>-5.431343045764688</v>
+        <v>-5.947247917366412</v>
       </c>
       <c r="G68">
-        <v>-5.259133794354542</v>
+        <v>-5.959463150459665</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.249844999513242</v>
       </c>
       <c r="E69">
-        <v>-7.088218659583667</v>
+        <v>-8.931389093237641</v>
       </c>
       <c r="F69">
-        <v>-5.730794911373725</v>
+        <v>-5.933550444903776</v>
       </c>
       <c r="G69">
-        <v>-5.271356328485531</v>
+        <v>-6.065741593906888</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.116162931206414</v>
       </c>
       <c r="E70">
-        <v>-7.50975619106167</v>
+        <v>-10.05347249675423</v>
       </c>
       <c r="F70">
-        <v>-5.855863334927809</v>
+        <v>-5.946655611354037</v>
       </c>
       <c r="G70">
-        <v>-5.833543240327946</v>
+        <v>-6.475722864035771</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.996191172119575</v>
       </c>
       <c r="E71">
-        <v>-7.731565376431372</v>
+        <v>-8.906853821064082</v>
       </c>
       <c r="F71">
-        <v>-5.692283934627985</v>
+        <v>-6.038657047246703</v>
       </c>
       <c r="G71">
-        <v>-5.509000529476574</v>
+        <v>-5.814875074031995</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.899922682348566</v>
       </c>
       <c r="E72">
-        <v>-7.75019099002492</v>
+        <v>-9.419993324769242</v>
       </c>
       <c r="F72">
-        <v>-6.041019144619582</v>
+        <v>-6.334211016671365</v>
       </c>
       <c r="G72">
-        <v>-5.13390578824053</v>
+        <v>-5.756937216549211</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.828305701116209</v>
       </c>
       <c r="E73">
-        <v>-7.877269027628166</v>
+        <v>-9.624100705242959</v>
       </c>
       <c r="F73">
-        <v>-6.162371006316608</v>
+        <v>-6.105627219292892</v>
       </c>
       <c r="G73">
-        <v>-5.186321655763811</v>
+        <v>-5.415593487086038</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.775596493634126</v>
       </c>
       <c r="E74">
-        <v>-7.920701621835732</v>
+        <v>-9.93505742992766</v>
       </c>
       <c r="F74">
-        <v>-6.112859608282225</v>
+        <v>-6.051352033864866</v>
       </c>
       <c r="G74">
-        <v>-4.590615470336275</v>
+        <v>-5.245719463829415</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.73615069380341</v>
       </c>
       <c r="E75">
-        <v>-8.100287315557916</v>
+        <v>-9.262135249335861</v>
       </c>
       <c r="F75">
-        <v>-6.208005888196475</v>
+        <v>-6.383480503627165</v>
       </c>
       <c r="G75">
-        <v>-4.759867111031514</v>
+        <v>-5.117108080174268</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.69420298810494</v>
       </c>
       <c r="E76">
-        <v>-8.236454000494556</v>
+        <v>-10.42472585285106</v>
       </c>
       <c r="F76">
-        <v>-6.030866005995699</v>
+        <v>-6.452644108366237</v>
       </c>
       <c r="G76">
-        <v>-5.699145023070153</v>
+        <v>-4.974410325249523</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.63865858287327</v>
       </c>
       <c r="E77">
-        <v>-8.691511296577334</v>
+        <v>-11.35297698341734</v>
       </c>
       <c r="F77">
-        <v>-6.088105097044469</v>
+        <v>-6.596096190186742</v>
       </c>
       <c r="G77">
-        <v>-4.283079031920139</v>
+        <v>-4.977820187154973</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.556176898848081</v>
       </c>
       <c r="E78">
-        <v>-9.387266043115808</v>
+        <v>-11.18108516703419</v>
       </c>
       <c r="F78">
-        <v>-6.294897496952975</v>
+        <v>-6.655998282732323</v>
       </c>
       <c r="G78">
-        <v>-4.226839484299</v>
+        <v>-4.696268220676576</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-3.433713599744027</v>
       </c>
       <c r="E79">
-        <v>-10.47957473003197</v>
+        <v>-11.44172148854566</v>
       </c>
       <c r="F79">
-        <v>-6.495700321089289</v>
+        <v>-6.903195375734957</v>
       </c>
       <c r="G79">
-        <v>-4.603033326654081</v>
+        <v>-4.918525006001087</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.264876769153944</v>
       </c>
       <c r="E80">
-        <v>-10.65158428673932</v>
+        <v>-12.08160392277749</v>
       </c>
       <c r="F80">
-        <v>-6.748957068850872</v>
+        <v>-6.585656004865686</v>
       </c>
       <c r="G80">
-        <v>-4.559969750279242</v>
+        <v>-4.225988674095407</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.043017910289599</v>
       </c>
       <c r="E81">
-        <v>-11.51633262629603</v>
+        <v>-13.00179436961012</v>
       </c>
       <c r="F81">
-        <v>-6.523461498007506</v>
+        <v>-6.957980910394233</v>
       </c>
       <c r="G81">
-        <v>-3.752461482340214</v>
+        <v>-4.743224998605599</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.770233942086221</v>
       </c>
       <c r="E82">
-        <v>-12.29407086626937</v>
+        <v>-12.88998181788673</v>
       </c>
       <c r="F82">
-        <v>-6.533077760326054</v>
+        <v>-6.747254980918254</v>
       </c>
       <c r="G82">
-        <v>-3.55874491010976</v>
+        <v>-4.144549253829336</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.4528452177403</v>
       </c>
       <c r="E83">
-        <v>-14.3058318587549</v>
+        <v>-13.37677918828927</v>
       </c>
       <c r="F83">
-        <v>-6.784430101724322</v>
+        <v>-7.243351650782619</v>
       </c>
       <c r="G83">
-        <v>-3.773490067605664</v>
+        <v>-3.715042386109832</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.099599285289488</v>
       </c>
       <c r="E84">
-        <v>-13.66475390738504</v>
+        <v>-14.50753461953055</v>
       </c>
       <c r="F84">
-        <v>-6.716628879999007</v>
+        <v>-7.009859156919241</v>
       </c>
       <c r="G84">
-        <v>-3.352484680831008</v>
+        <v>-3.607863474275927</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.72708547588263</v>
       </c>
       <c r="E85">
-        <v>-15.09642643643602</v>
+        <v>-16.39092695932065</v>
       </c>
       <c r="F85">
-        <v>-7.105587052830936</v>
+        <v>-7.036415133635808</v>
       </c>
       <c r="G85">
-        <v>-3.108626585862754</v>
+        <v>-3.35702012821981</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-1.351242854708326</v>
       </c>
       <c r="E86">
-        <v>-16.00324429952399</v>
+        <v>-16.49268177027301</v>
       </c>
       <c r="F86">
-        <v>-7.246079188295485</v>
+        <v>-7.360234690312754</v>
       </c>
       <c r="G86">
-        <v>-3.418460542883144</v>
+        <v>-3.64418677993281</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.9954979925424767</v>
       </c>
       <c r="E87">
-        <v>-17.7150754015335</v>
+        <v>-18.96323152142364</v>
       </c>
       <c r="F87">
-        <v>-7.524828850177897</v>
+        <v>-7.190743711757072</v>
       </c>
       <c r="G87">
-        <v>-2.599232943735096</v>
+        <v>-4.001212563615511</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-0.6862057018534085</v>
       </c>
       <c r="E88">
-        <v>-19.6216082435028</v>
+        <v>-20.79475019145588</v>
       </c>
       <c r="F88">
-        <v>-7.402792827525401</v>
+        <v>-7.498323156124145</v>
       </c>
       <c r="G88">
-        <v>-3.306160217099987</v>
+        <v>-3.574814298157383</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-0.4449869581639694</v>
       </c>
       <c r="E89">
-        <v>-20.42457914064688</v>
+        <v>-20.82911225222608</v>
       </c>
       <c r="F89">
-        <v>-7.346586312733497</v>
+        <v>-7.775820106627445</v>
       </c>
       <c r="G89">
-        <v>-2.996008447707826</v>
+        <v>-4.276881690670623</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-0.2984640283106973</v>
       </c>
       <c r="E90">
-        <v>-21.8372683066577</v>
+        <v>-23.4868691188538</v>
       </c>
       <c r="F90">
-        <v>-7.358304548728312</v>
+        <v>-7.437952286627593</v>
       </c>
       <c r="G90">
-        <v>-3.63101742977759</v>
+        <v>-3.424727405588984</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-0.2624517064011256</v>
       </c>
       <c r="E91">
-        <v>-24.02094375789642</v>
+        <v>-25.25418308440529</v>
       </c>
       <c r="F91">
-        <v>-7.487661647901406</v>
+        <v>-7.672222776021931</v>
       </c>
       <c r="G91">
-        <v>-4.298906750143394</v>
+        <v>-3.589562778534836</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-0.3547120260948307</v>
       </c>
       <c r="E92">
-        <v>-26.21768385664727</v>
+        <v>-26.96044869185937</v>
       </c>
       <c r="F92">
-        <v>-7.563792370888975</v>
+        <v>-8.043620025810508</v>
       </c>
       <c r="G92">
-        <v>-4.006681584846388</v>
+        <v>-4.048162720453456</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-0.5893800540079395</v>
       </c>
       <c r="E93">
-        <v>-28.31078982773259</v>
+        <v>-29.35712091804887</v>
       </c>
       <c r="F93">
-        <v>-7.575796465801527</v>
+        <v>-7.859882028839534</v>
       </c>
       <c r="G93">
-        <v>-4.029100599238332</v>
+        <v>-5.143767903402019</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-0.9676908196188015</v>
       </c>
       <c r="E94">
-        <v>-29.93209899856577</v>
+        <v>-31.01125246848965</v>
       </c>
       <c r="F94">
-        <v>-7.857158450591457</v>
+        <v>-7.753023451827652</v>
       </c>
       <c r="G94">
-        <v>-4.36915321594119</v>
+        <v>-3.807836977575603</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.492940586003276</v>
       </c>
       <c r="E95">
-        <v>-31.62494673753513</v>
+        <v>-32.9932681794558</v>
       </c>
       <c r="F95">
-        <v>-7.386353564196661</v>
+        <v>-7.620312459452136</v>
       </c>
       <c r="G95">
-        <v>-4.693268866417996</v>
+        <v>-5.144569055422523</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-2.159876951718293</v>
       </c>
       <c r="E96">
-        <v>-35.14696739700075</v>
+        <v>-35.52384738205211</v>
       </c>
       <c r="F96">
-        <v>-7.004006967635213</v>
+        <v>-7.32342303001428</v>
       </c>
       <c r="G96">
-        <v>-4.641369443998842</v>
+        <v>-5.492067089043202</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.9433746279144</v>
       </c>
       <c r="E97">
-        <v>-37.53502872986466</v>
+        <v>-37.16153151489703</v>
       </c>
       <c r="F97">
-        <v>-7.552378206429924</v>
+        <v>-7.618599681504588</v>
       </c>
       <c r="G97">
-        <v>-5.69975416344938</v>
+        <v>-6.113972931868529</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.84001101647897</v>
       </c>
       <c r="E98">
-        <v>-40.54169093336137</v>
+        <v>-38.75786615157791</v>
       </c>
       <c r="F98">
-        <v>-7.046519969229269</v>
+        <v>-7.651136523610813</v>
       </c>
       <c r="G98">
-        <v>-5.83343068177961</v>
+        <v>-6.195366004497052</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.782096048299977</v>
       </c>
       <c r="E99">
-        <v>-42.01682096322695</v>
+        <v>-42.02837083618351</v>
       </c>
       <c r="F99">
-        <v>-6.971539808589267</v>
+        <v>-7.368093434991644</v>
       </c>
       <c r="G99">
-        <v>-6.451314211774725</v>
+        <v>-7.401252080449817</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-5.781584134791371</v>
       </c>
       <c r="E100">
-        <v>-43.74152878107727</v>
+        <v>-43.90851852434712</v>
       </c>
       <c r="F100">
-        <v>-6.708519513859</v>
+        <v>-6.946547741464197</v>
       </c>
       <c r="G100">
-        <v>-7.473504736844411</v>
+        <v>-7.422105206801686</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-6.718600936341557</v>
       </c>
       <c r="E101">
-        <v>-47.15312713033986</v>
+        <v>-47.79587156014454</v>
       </c>
       <c r="F101">
-        <v>-6.58908552002557</v>
+        <v>-6.976357837910514</v>
       </c>
       <c r="G101">
-        <v>-7.820953112282</v>
+        <v>-7.256485234563027</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-7.681801727985111</v>
       </c>
       <c r="E102">
-        <v>-49.79338710552044</v>
+        <v>-49.73678231254307</v>
       </c>
       <c r="F102">
-        <v>-6.358150711215627</v>
+        <v>-7.309533533209397</v>
       </c>
       <c r="G102">
-        <v>-7.666863770156622</v>
+        <v>-7.616384571773816</v>
       </c>
     </row>
   </sheetData>
